--- a/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25E56BDB-27CA-4BF0-B36B-1877AA757A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57ADE50B-69AD-40BE-AD5A-0085354E2520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="87">
   <si>
     <t>击中回血固定值</t>
   </si>
@@ -331,6 +331,10 @@
   </si>
   <si>
     <t>击杀回血效果提高</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>杀怪掉落血瓶回复生命</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -916,7 +920,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85CB23A7-FBFE-4C22-A658-7D7AF331C130}">
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" bestFit="1" customWidth="1"/>
@@ -2211,6 +2215,21 @@
         <v>0</v>
       </c>
     </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A77" s="12">
+        <v>4590900</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C77" s="7"/>
+      <c r="D77" s="12">
+        <v>30001</v>
+      </c>
+      <c r="E77" s="12">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A4:E74" xr:uid="{85CB23A7-FBFE-4C22-A658-7D7AF331C130}"/>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57ADE50B-69AD-40BE-AD5A-0085354E2520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E937887-6A4C-4DD2-93C9-D20768F1CF85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attr_skill_v8" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="110">
   <si>
     <t>击中回血固定值</t>
   </si>
@@ -335,6 +335,98 @@
   </si>
   <si>
     <t>杀怪掉落血瓶回复生命</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>拥有正义光环时-每秒释放-自身光环范围提高、敌人受到全属性伤害提高、敌人全属性伤害降低</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击次数—触发释放—技能重击</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击暴击后—触发释放—自身暴击伤害提高状态、自身攻速提高、攻击次数计数+1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击命中后，目标血量低于百万分比—触发释放—斩杀</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击暴击后，目标血量低于百万分比—触发释放—斩杀</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>desc1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击次数—触发释放—冰霜新星</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放冰霜新星—触发释放—冰霜新星</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击次数—触发释放—陨石</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀燃烧目标—触发释放—死亡爆炸</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击次数—触发释放—闪电链</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成触电伤害时—触发释放—电磁爆炸</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击次数—触发释放—传染</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀中毒目标—触发释放—瘟疫</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>每损失%血量时—触发释放—获得护盾</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>有护盾时—每秒释放—受到全属性伤害降低</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀目标—触发释放—回复生命值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命全满时—每秒释放—全属性伤害提升</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命值低于百万分比时—每秒释放—受到全属性伤害降低</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>死亡时—触发释放—技能复活</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击—触发释放—技能多重打击</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击—触发释放—旋风斩</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>旋风斩—触发释放—半月斩</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -920,7 +1012,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85CB23A7-FBFE-4C22-A658-7D7AF331C130}">
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" bestFit="1" customWidth="1"/>
@@ -928,10 +1020,11 @@
     <col min="3" max="3" width="7.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="6" max="6" width="70.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="6" t="s">
         <v>10</v>
       </c>
@@ -940,7 +1033,7 @@
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
@@ -956,8 +1049,11 @@
       <c r="E2" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F2" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
         <v>6</v>
       </c>
@@ -973,8 +1069,11 @@
       <c r="E3" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F3" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
@@ -990,8 +1089,9 @@
       <c r="E4" s="6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" s="2">
         <v>3041101</v>
       </c>
@@ -1007,8 +1107,9 @@
       <c r="E5" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" s="14">
         <v>3540100</v>
       </c>
@@ -1024,8 +1125,9 @@
       <c r="E6" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7" s="14">
         <v>3540300</v>
       </c>
@@ -1041,8 +1143,9 @@
       <c r="E7" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A8" s="14">
         <v>3540500</v>
       </c>
@@ -1058,8 +1161,9 @@
       <c r="E8" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F8" s="7"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9" s="14">
         <v>3540700</v>
       </c>
@@ -1075,8 +1179,9 @@
       <c r="E9" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F9" s="7"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A10" s="14">
         <v>3540900</v>
       </c>
@@ -1092,8 +1197,9 @@
       <c r="E10" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A11" s="14">
         <v>3541100</v>
       </c>
@@ -1109,8 +1215,9 @@
       <c r="E11" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F11" s="7"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A12" s="14">
         <v>3541300</v>
       </c>
@@ -1126,8 +1233,9 @@
       <c r="E12" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F12" s="7"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A13" s="14">
         <v>3541500</v>
       </c>
@@ -1143,8 +1251,9 @@
       <c r="E13" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A14" s="14">
         <v>3541700</v>
       </c>
@@ -1160,8 +1269,9 @@
       <c r="E14" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A15" s="14">
         <v>3541900</v>
       </c>
@@ -1177,8 +1287,9 @@
       <c r="E15" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A16" s="14">
         <v>3542100</v>
       </c>
@@ -1194,8 +1305,9 @@
       <c r="E16" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F16" s="7"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A17" s="14">
         <v>3542300</v>
       </c>
@@ -1211,8 +1323,9 @@
       <c r="E17" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F17" s="7"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A18" s="14">
         <v>3542500</v>
       </c>
@@ -1228,8 +1341,9 @@
       <c r="E18" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A19" s="13">
         <v>3550100</v>
       </c>
@@ -1245,8 +1359,9 @@
       <c r="E19" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F19" s="7"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A20" s="13">
         <v>3550400</v>
       </c>
@@ -1260,10 +1375,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="13">
-        <v>55020001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
+        <v>550001</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A21" s="13">
         <v>3550600</v>
       </c>
@@ -1277,10 +1395,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="13">
-        <v>55030001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
+        <v>550002</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A22" s="13">
         <v>3550800</v>
       </c>
@@ -1296,8 +1417,9 @@
       <c r="E22" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F22" s="7"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A23" s="13">
         <v>3551000</v>
       </c>
@@ -1313,8 +1435,9 @@
       <c r="E23" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F23" s="7"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A24" s="13">
         <v>3551200</v>
       </c>
@@ -1330,8 +1453,9 @@
       <c r="E24" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F24" s="7"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A25" s="13">
         <v>3551400</v>
       </c>
@@ -1347,8 +1471,9 @@
       <c r="E25" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F25" s="7"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A26" s="13">
         <v>3550300</v>
       </c>
@@ -1364,8 +1489,9 @@
       <c r="E26" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F26" s="7"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A27" s="3">
         <v>3560100</v>
       </c>
@@ -1381,8 +1507,9 @@
       <c r="E27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F27" s="7"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A28" s="3">
         <v>3560400</v>
       </c>
@@ -1396,10 +1523,13 @@
         <v>0</v>
       </c>
       <c r="E28" s="3">
-        <v>56040001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
+        <v>560001</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A29" s="3">
         <v>3560600</v>
       </c>
@@ -1415,8 +1545,9 @@
       <c r="E29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F29" s="7"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A30" s="3">
         <v>3560800</v>
       </c>
@@ -1432,8 +1563,9 @@
       <c r="E30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F30" s="7"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A31" s="3">
         <v>3561000</v>
       </c>
@@ -1447,10 +1579,13 @@
         <v>0</v>
       </c>
       <c r="E31" s="3">
-        <v>56100001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
+        <v>560002</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A32" s="3">
         <v>3561300</v>
       </c>
@@ -1466,8 +1601,9 @@
       <c r="E32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A33" s="3">
         <v>3560300</v>
       </c>
@@ -1483,8 +1619,9 @@
       <c r="E33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A34" s="3">
         <v>3561200</v>
       </c>
@@ -1500,8 +1637,9 @@
       <c r="E34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A35" s="4">
         <v>3570100</v>
       </c>
@@ -1517,8 +1655,9 @@
       <c r="E35" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F35" s="7"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A36" s="4">
         <v>3570400</v>
       </c>
@@ -1534,8 +1673,9 @@
       <c r="E36" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F36" s="7"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A37" s="4">
         <v>3570600</v>
       </c>
@@ -1549,10 +1689,13 @@
         <v>0</v>
       </c>
       <c r="E37" s="4">
-        <v>57060001</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
+        <v>570001</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A38" s="4">
         <v>3570800</v>
       </c>
@@ -1568,8 +1711,9 @@
       <c r="E38" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F38" s="7"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A39" s="4">
         <v>3571000</v>
       </c>
@@ -1585,8 +1729,9 @@
       <c r="E39" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F39" s="7"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A40" s="4">
         <v>3571200</v>
       </c>
@@ -1600,10 +1745,13 @@
         <v>0</v>
       </c>
       <c r="E40" s="4">
-        <v>57120001</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.15">
+        <v>570002</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A41" s="4">
         <v>3570300</v>
       </c>
@@ -1619,8 +1767,9 @@
       <c r="E41" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F41" s="7"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A42" s="4">
         <v>3571400</v>
       </c>
@@ -1636,8 +1785,9 @@
       <c r="E42" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F42" s="7"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A43" s="5">
         <v>3580100</v>
       </c>
@@ -1653,8 +1803,9 @@
       <c r="E43" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F43" s="7"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A44" s="5">
         <v>3580400</v>
       </c>
@@ -1668,10 +1819,13 @@
         <v>0</v>
       </c>
       <c r="E44" s="5">
-        <v>58040001</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.15">
+        <v>580001</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A45" s="5">
         <v>3580600</v>
       </c>
@@ -1687,8 +1841,9 @@
       <c r="E45" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F45" s="7"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A46" s="5">
         <v>3580800</v>
       </c>
@@ -1702,10 +1857,13 @@
         <v>0</v>
       </c>
       <c r="E46" s="5">
-        <v>58080001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.15">
+        <v>580002</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A47" s="5">
         <v>3581200</v>
       </c>
@@ -1721,8 +1879,9 @@
       <c r="E47" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F47" s="7"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A48" s="5">
         <v>3580300</v>
       </c>
@@ -1738,8 +1897,9 @@
       <c r="E48" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F48" s="7"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A49" s="5">
         <v>3581000</v>
       </c>
@@ -1755,8 +1915,9 @@
       <c r="E49" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F49" s="7"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A50" s="9">
         <v>3590100</v>
       </c>
@@ -1770,10 +1931,13 @@
         <v>0</v>
       </c>
       <c r="E50" s="9">
-        <v>59010001</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.15">
+        <v>590001</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A51" s="10">
         <v>3590300</v>
       </c>
@@ -1789,8 +1953,9 @@
       <c r="E51" s="10">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F51" s="7"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A52" s="9">
         <v>3590500</v>
       </c>
@@ -1804,10 +1969,13 @@
         <v>0</v>
       </c>
       <c r="E52" s="9">
-        <v>59050001</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.15">
+        <v>590002</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A53" s="9">
         <v>3590700</v>
       </c>
@@ -1821,10 +1989,13 @@
         <v>0</v>
       </c>
       <c r="E53" s="9">
-        <v>59070001</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.15">
+        <v>590003</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A54" s="9">
         <v>3590900</v>
       </c>
@@ -1840,8 +2011,9 @@
       <c r="E54" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F54" s="7"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A55" s="10">
         <v>3591100</v>
       </c>
@@ -1855,10 +2027,13 @@
         <v>0</v>
       </c>
       <c r="E55" s="10">
-        <v>59110001</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.15">
+        <v>590004</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A56" s="9">
         <v>3591300</v>
       </c>
@@ -1872,10 +2047,13 @@
         <v>0</v>
       </c>
       <c r="E56" s="9">
-        <v>59130001</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.15">
+        <v>590005</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A57" s="9">
         <v>3591500</v>
       </c>
@@ -1889,10 +2067,13 @@
         <v>0</v>
       </c>
       <c r="E57" s="9">
-        <v>59150001</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.15">
+        <v>590006</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A58" s="9">
         <v>3591800</v>
       </c>
@@ -1908,8 +2089,9 @@
       <c r="E58" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F58" s="7"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A59" s="9">
         <v>3592000</v>
       </c>
@@ -1925,8 +2107,9 @@
       <c r="E59" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F59" s="7"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A60" s="9">
         <v>3591700</v>
       </c>
@@ -1942,8 +2125,9 @@
       <c r="E60" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F60" s="7"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A61" s="11">
         <v>3600100</v>
       </c>
@@ -1957,10 +2141,13 @@
         <v>0</v>
       </c>
       <c r="E61" s="11">
-        <v>60010001</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.15">
+        <v>600001</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A62" s="11">
         <v>3600300</v>
       </c>
@@ -1976,8 +2163,9 @@
       <c r="E62" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F62" s="7"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A63" s="11">
         <v>3600600</v>
       </c>
@@ -1991,10 +2179,13 @@
         <v>0</v>
       </c>
       <c r="E63" s="11">
-        <v>60060001</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.15">
+        <v>600002</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A64" s="11">
         <v>3600900</v>
       </c>
@@ -2008,10 +2199,13 @@
         <v>0</v>
       </c>
       <c r="E64" s="11">
-        <v>60090001</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.15">
+        <v>600003</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A65" s="11">
         <v>3601200</v>
       </c>
@@ -2022,13 +2216,16 @@
         <v>60110001</v>
       </c>
       <c r="D65" s="11">
-        <v>60110001</v>
+        <v>0</v>
       </c>
       <c r="E65" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.15">
+        <v>600004</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A66" s="11">
         <v>3600500</v>
       </c>
@@ -2044,8 +2241,9 @@
       <c r="E66" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F66" s="7"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A67" s="11">
         <v>3600800</v>
       </c>
@@ -2061,8 +2259,9 @@
       <c r="E67" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F67" s="7"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A68" s="12">
         <v>3610200</v>
       </c>
@@ -2076,10 +2275,13 @@
         <v>0</v>
       </c>
       <c r="E68" s="12">
-        <v>61020001</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.15">
+        <v>610001</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A69" s="12">
         <v>3610400</v>
       </c>
@@ -2095,8 +2297,9 @@
       <c r="E69" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F69" s="7"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A70" s="12">
         <v>3610600</v>
       </c>
@@ -2110,10 +2313,13 @@
         <v>0</v>
       </c>
       <c r="E70" s="12">
-        <v>61060001</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.15">
+        <v>610002</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A71" s="12">
         <v>3610800</v>
       </c>
@@ -2129,8 +2335,9 @@
       <c r="E71" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F71" s="7"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A72" s="12">
         <v>3611000</v>
       </c>
@@ -2146,8 +2353,9 @@
       <c r="E72" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F72" s="7"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A73" s="12">
         <v>3611200</v>
       </c>
@@ -2163,8 +2371,9 @@
       <c r="E73" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F73" s="7"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A74" s="12">
         <v>3611400</v>
       </c>
@@ -2178,10 +2387,13 @@
         <v>0</v>
       </c>
       <c r="E74" s="12">
-        <v>61140001</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.15">
+        <v>610003</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A75" s="12">
         <v>3611600</v>
       </c>
@@ -2195,10 +2407,13 @@
         <v>0</v>
       </c>
       <c r="E75" s="12">
-        <v>61160001</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.15">
+        <v>610004</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A76" s="12">
         <v>3610100</v>
       </c>
@@ -2214,8 +2429,9 @@
       <c r="E76" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F76" s="7"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A77" s="12">
         <v>4590900</v>
       </c>
@@ -2229,6 +2445,7 @@
       <c r="E77" s="12">
         <v>0</v>
       </c>
+      <c r="F77" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:E74" xr:uid="{85CB23A7-FBFE-4C22-A658-7D7AF331C130}"/>

--- a/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E937887-6A4C-4DD2-93C9-D20768F1CF85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06B66ED3-BEC6-4779-AA92-A4E1B8BDDFDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attr_skill_v8" sheetId="1" r:id="rId1"/>
@@ -30,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -39,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="88">
   <si>
     <t>击中回血固定值</t>
   </si>
@@ -338,95 +336,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>拥有正义光环时-每秒释放-自身光环范围提高、敌人受到全属性伤害提高、敌人全属性伤害降低</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击次数—触发释放—技能重击</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击暴击后—触发释放—自身暴击伤害提高状态、自身攻速提高、攻击次数计数+1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击命中后，目标血量低于百万分比—触发释放—斩杀</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击暴击后，目标血量低于百万分比—触发释放—斩杀</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>desc1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击次数—触发释放—冰霜新星</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>释放冰霜新星—触发释放—冰霜新星</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击次数—触发释放—陨石</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀燃烧目标—触发释放—死亡爆炸</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击次数—触发释放—闪电链</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成触电伤害时—触发释放—电磁爆炸</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击次数—触发释放—传染</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀中毒目标—触发释放—瘟疫</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>每损失%血量时—触发释放—获得护盾</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>有护盾时—每秒释放—受到全属性伤害降低</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀目标—触发释放—回复生命值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>生命全满时—每秒释放—全属性伤害提升</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>生命值低于百万分比时—每秒释放—受到全属性伤害降低</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>死亡时—触发释放—技能复活</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击—触发释放—技能多重打击</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击—触发释放—旋风斩</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>旋风斩—触发释放—半月斩</t>
+    <t>每8秒获得自身生命上限20%的护盾值，持续4秒</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1012,19 +922,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85CB23A7-FBFE-4C22-A658-7D7AF331C130}">
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="64.625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.25" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="70.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A1" s="6" t="s">
         <v>10</v>
       </c>
@@ -1033,7 +942,7 @@
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
@@ -1049,11 +958,8 @@
       <c r="E2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
         <v>6</v>
       </c>
@@ -1069,11 +975,8 @@
       <c r="E3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
@@ -1089,9 +992,8 @@
       <c r="E4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="7"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" s="2">
         <v>3041101</v>
       </c>
@@ -1107,9 +1009,8 @@
       <c r="E5" s="2">
         <v>0</v>
       </c>
-      <c r="F5" s="7"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" s="14">
         <v>3540100</v>
       </c>
@@ -1125,9 +1026,8 @@
       <c r="E6" s="14">
         <v>0</v>
       </c>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="14">
         <v>3540300</v>
       </c>
@@ -1143,9 +1043,8 @@
       <c r="E7" s="14">
         <v>0</v>
       </c>
-      <c r="F7" s="7"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8" s="14">
         <v>3540500</v>
       </c>
@@ -1161,9 +1060,8 @@
       <c r="E8" s="14">
         <v>0</v>
       </c>
-      <c r="F8" s="7"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9" s="14">
         <v>3540700</v>
       </c>
@@ -1179,9 +1077,8 @@
       <c r="E9" s="14">
         <v>0</v>
       </c>
-      <c r="F9" s="7"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10" s="14">
         <v>3540900</v>
       </c>
@@ -1197,9 +1094,8 @@
       <c r="E10" s="14">
         <v>0</v>
       </c>
-      <c r="F10" s="7"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11" s="14">
         <v>3541100</v>
       </c>
@@ -1215,9 +1111,8 @@
       <c r="E11" s="14">
         <v>0</v>
       </c>
-      <c r="F11" s="7"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12" s="14">
         <v>3541300</v>
       </c>
@@ -1233,9 +1128,8 @@
       <c r="E12" s="14">
         <v>0</v>
       </c>
-      <c r="F12" s="7"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13" s="14">
         <v>3541500</v>
       </c>
@@ -1251,9 +1145,8 @@
       <c r="E13" s="14">
         <v>0</v>
       </c>
-      <c r="F13" s="7"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A14" s="14">
         <v>3541700</v>
       </c>
@@ -1269,9 +1162,8 @@
       <c r="E14" s="14">
         <v>0</v>
       </c>
-      <c r="F14" s="7"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A15" s="14">
         <v>3541900</v>
       </c>
@@ -1287,9 +1179,8 @@
       <c r="E15" s="14">
         <v>0</v>
       </c>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A16" s="14">
         <v>3542100</v>
       </c>
@@ -1305,9 +1196,8 @@
       <c r="E16" s="14">
         <v>0</v>
       </c>
-      <c r="F16" s="7"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A17" s="14">
         <v>3542300</v>
       </c>
@@ -1323,9 +1213,8 @@
       <c r="E17" s="14">
         <v>0</v>
       </c>
-      <c r="F17" s="7"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A18" s="14">
         <v>3542500</v>
       </c>
@@ -1341,9 +1230,8 @@
       <c r="E18" s="14">
         <v>0</v>
       </c>
-      <c r="F18" s="7"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A19" s="13">
         <v>3550100</v>
       </c>
@@ -1359,9 +1247,8 @@
       <c r="E19" s="13">
         <v>0</v>
       </c>
-      <c r="F19" s="7"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A20" s="13">
         <v>3550400</v>
       </c>
@@ -1377,11 +1264,8 @@
       <c r="E20" s="13">
         <v>550001</v>
       </c>
-      <c r="F20" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A21" s="13">
         <v>3550600</v>
       </c>
@@ -1397,11 +1281,8 @@
       <c r="E21" s="13">
         <v>550002</v>
       </c>
-      <c r="F21" s="7" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A22" s="13">
         <v>3550800</v>
       </c>
@@ -1417,9 +1298,8 @@
       <c r="E22" s="13">
         <v>0</v>
       </c>
-      <c r="F22" s="7"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A23" s="13">
         <v>3551000</v>
       </c>
@@ -1435,9 +1315,8 @@
       <c r="E23" s="13">
         <v>0</v>
       </c>
-      <c r="F23" s="7"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A24" s="13">
         <v>3551200</v>
       </c>
@@ -1453,9 +1332,8 @@
       <c r="E24" s="13">
         <v>0</v>
       </c>
-      <c r="F24" s="7"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A25" s="13">
         <v>3551400</v>
       </c>
@@ -1471,9 +1349,8 @@
       <c r="E25" s="13">
         <v>0</v>
       </c>
-      <c r="F25" s="7"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A26" s="13">
         <v>3550300</v>
       </c>
@@ -1489,9 +1366,8 @@
       <c r="E26" s="13">
         <v>0</v>
       </c>
-      <c r="F26" s="7"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A27" s="3">
         <v>3560100</v>
       </c>
@@ -1507,9 +1383,8 @@
       <c r="E27" s="3">
         <v>0</v>
       </c>
-      <c r="F27" s="7"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A28" s="3">
         <v>3560400</v>
       </c>
@@ -1525,11 +1400,8 @@
       <c r="E28" s="3">
         <v>560001</v>
       </c>
-      <c r="F28" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A29" s="3">
         <v>3560600</v>
       </c>
@@ -1545,9 +1417,8 @@
       <c r="E29" s="3">
         <v>0</v>
       </c>
-      <c r="F29" s="7"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A30" s="3">
         <v>3560800</v>
       </c>
@@ -1563,9 +1434,8 @@
       <c r="E30" s="3">
         <v>0</v>
       </c>
-      <c r="F30" s="7"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A31" s="3">
         <v>3561000</v>
       </c>
@@ -1581,11 +1451,8 @@
       <c r="E31" s="3">
         <v>560002</v>
       </c>
-      <c r="F31" s="7" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A32" s="3">
         <v>3561300</v>
       </c>
@@ -1601,9 +1468,8 @@
       <c r="E32" s="3">
         <v>0</v>
       </c>
-      <c r="F32" s="7"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A33" s="3">
         <v>3560300</v>
       </c>
@@ -1619,9 +1485,8 @@
       <c r="E33" s="3">
         <v>0</v>
       </c>
-      <c r="F33" s="7"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A34" s="3">
         <v>3561200</v>
       </c>
@@ -1637,9 +1502,8 @@
       <c r="E34" s="3">
         <v>0</v>
       </c>
-      <c r="F34" s="7"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A35" s="4">
         <v>3570100</v>
       </c>
@@ -1655,9 +1519,8 @@
       <c r="E35" s="4">
         <v>0</v>
       </c>
-      <c r="F35" s="7"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A36" s="4">
         <v>3570400</v>
       </c>
@@ -1673,9 +1536,8 @@
       <c r="E36" s="4">
         <v>0</v>
       </c>
-      <c r="F36" s="7"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A37" s="4">
         <v>3570600</v>
       </c>
@@ -1691,11 +1553,8 @@
       <c r="E37" s="4">
         <v>570001</v>
       </c>
-      <c r="F37" s="7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A38" s="4">
         <v>3570800</v>
       </c>
@@ -1711,9 +1570,8 @@
       <c r="E38" s="4">
         <v>0</v>
       </c>
-      <c r="F38" s="7"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A39" s="4">
         <v>3571000</v>
       </c>
@@ -1729,9 +1587,8 @@
       <c r="E39" s="4">
         <v>0</v>
       </c>
-      <c r="F39" s="7"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A40" s="4">
         <v>3571200</v>
       </c>
@@ -1747,11 +1604,8 @@
       <c r="E40" s="4">
         <v>570002</v>
       </c>
-      <c r="F40" s="7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A41" s="4">
         <v>3570300</v>
       </c>
@@ -1767,9 +1621,8 @@
       <c r="E41" s="4">
         <v>0</v>
       </c>
-      <c r="F41" s="7"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A42" s="4">
         <v>3571400</v>
       </c>
@@ -1785,9 +1638,8 @@
       <c r="E42" s="4">
         <v>0</v>
       </c>
-      <c r="F42" s="7"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A43" s="5">
         <v>3580100</v>
       </c>
@@ -1803,9 +1655,8 @@
       <c r="E43" s="5">
         <v>0</v>
       </c>
-      <c r="F43" s="7"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A44" s="5">
         <v>3580400</v>
       </c>
@@ -1821,11 +1672,8 @@
       <c r="E44" s="5">
         <v>580001</v>
       </c>
-      <c r="F44" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A45" s="5">
         <v>3580600</v>
       </c>
@@ -1841,9 +1689,8 @@
       <c r="E45" s="5">
         <v>0</v>
       </c>
-      <c r="F45" s="7"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A46" s="5">
         <v>3580800</v>
       </c>
@@ -1859,11 +1706,8 @@
       <c r="E46" s="5">
         <v>580002</v>
       </c>
-      <c r="F46" s="7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A47" s="5">
         <v>3581200</v>
       </c>
@@ -1879,9 +1723,8 @@
       <c r="E47" s="5">
         <v>0</v>
       </c>
-      <c r="F47" s="7"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A48" s="5">
         <v>3580300</v>
       </c>
@@ -1897,9 +1740,8 @@
       <c r="E48" s="5">
         <v>0</v>
       </c>
-      <c r="F48" s="7"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A49" s="5">
         <v>3581000</v>
       </c>
@@ -1915,9 +1757,8 @@
       <c r="E49" s="5">
         <v>0</v>
       </c>
-      <c r="F49" s="7"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A50" s="9">
         <v>3590100</v>
       </c>
@@ -1933,11 +1774,8 @@
       <c r="E50" s="9">
         <v>590001</v>
       </c>
-      <c r="F50" s="7" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A51" s="10">
         <v>3590300</v>
       </c>
@@ -1953,9 +1791,8 @@
       <c r="E51" s="10">
         <v>0</v>
       </c>
-      <c r="F51" s="7"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A52" s="9">
         <v>3590500</v>
       </c>
@@ -1971,11 +1808,8 @@
       <c r="E52" s="9">
         <v>590002</v>
       </c>
-      <c r="F52" s="7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A53" s="9">
         <v>3590700</v>
       </c>
@@ -1991,11 +1825,8 @@
       <c r="E53" s="9">
         <v>590003</v>
       </c>
-      <c r="F53" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A54" s="9">
         <v>3590900</v>
       </c>
@@ -2011,9 +1842,8 @@
       <c r="E54" s="9">
         <v>0</v>
       </c>
-      <c r="F54" s="7"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A55" s="10">
         <v>3591100</v>
       </c>
@@ -2029,11 +1859,8 @@
       <c r="E55" s="10">
         <v>590004</v>
       </c>
-      <c r="F55" s="7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A56" s="9">
         <v>3591300</v>
       </c>
@@ -2049,11 +1876,8 @@
       <c r="E56" s="9">
         <v>590005</v>
       </c>
-      <c r="F56" s="7" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A57" s="9">
         <v>3591500</v>
       </c>
@@ -2069,11 +1893,8 @@
       <c r="E57" s="9">
         <v>590006</v>
       </c>
-      <c r="F57" s="7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A58" s="9">
         <v>3591800</v>
       </c>
@@ -2089,9 +1910,8 @@
       <c r="E58" s="9">
         <v>0</v>
       </c>
-      <c r="F58" s="7"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A59" s="9">
         <v>3592000</v>
       </c>
@@ -2107,9 +1927,8 @@
       <c r="E59" s="9">
         <v>0</v>
       </c>
-      <c r="F59" s="7"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A60" s="9">
         <v>3591700</v>
       </c>
@@ -2125,9 +1944,8 @@
       <c r="E60" s="9">
         <v>0</v>
       </c>
-      <c r="F60" s="7"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A61" s="11">
         <v>3600100</v>
       </c>
@@ -2143,11 +1961,8 @@
       <c r="E61" s="11">
         <v>600001</v>
       </c>
-      <c r="F61" s="7" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A62" s="11">
         <v>3600300</v>
       </c>
@@ -2163,9 +1978,8 @@
       <c r="E62" s="11">
         <v>0</v>
       </c>
-      <c r="F62" s="7"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A63" s="11">
         <v>3600600</v>
       </c>
@@ -2181,11 +1995,8 @@
       <c r="E63" s="11">
         <v>600002</v>
       </c>
-      <c r="F63" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A64" s="11">
         <v>3600900</v>
       </c>
@@ -2201,11 +2012,8 @@
       <c r="E64" s="11">
         <v>600003</v>
       </c>
-      <c r="F64" s="7" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A65" s="11">
         <v>3601200</v>
       </c>
@@ -2216,16 +2024,13 @@
         <v>60110001</v>
       </c>
       <c r="D65" s="11">
-        <v>0</v>
+        <v>60110001</v>
       </c>
       <c r="E65" s="11">
-        <v>600004</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A66" s="11">
         <v>3600500</v>
       </c>
@@ -2241,9 +2046,8 @@
       <c r="E66" s="11">
         <v>0</v>
       </c>
-      <c r="F66" s="7"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A67" s="11">
         <v>3600800</v>
       </c>
@@ -2259,9 +2063,8 @@
       <c r="E67" s="11">
         <v>0</v>
       </c>
-      <c r="F67" s="7"/>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A68" s="12">
         <v>3610200</v>
       </c>
@@ -2277,11 +2080,8 @@
       <c r="E68" s="12">
         <v>610001</v>
       </c>
-      <c r="F68" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A69" s="12">
         <v>3610400</v>
       </c>
@@ -2297,9 +2097,8 @@
       <c r="E69" s="12">
         <v>0</v>
       </c>
-      <c r="F69" s="7"/>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A70" s="12">
         <v>3610600</v>
       </c>
@@ -2315,11 +2114,8 @@
       <c r="E70" s="12">
         <v>610002</v>
       </c>
-      <c r="F70" s="7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A71" s="12">
         <v>3610800</v>
       </c>
@@ -2335,9 +2131,8 @@
       <c r="E71" s="12">
         <v>0</v>
       </c>
-      <c r="F71" s="7"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A72" s="12">
         <v>3611000</v>
       </c>
@@ -2353,9 +2148,8 @@
       <c r="E72" s="12">
         <v>0</v>
       </c>
-      <c r="F72" s="7"/>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A73" s="12">
         <v>3611200</v>
       </c>
@@ -2371,9 +2165,8 @@
       <c r="E73" s="12">
         <v>0</v>
       </c>
-      <c r="F73" s="7"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A74" s="12">
         <v>3611400</v>
       </c>
@@ -2389,11 +2182,8 @@
       <c r="E74" s="12">
         <v>610003</v>
       </c>
-      <c r="F74" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A75" s="12">
         <v>3611600</v>
       </c>
@@ -2409,11 +2199,8 @@
       <c r="E75" s="12">
         <v>610004</v>
       </c>
-      <c r="F75" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A76" s="12">
         <v>3610100</v>
       </c>
@@ -2429,9 +2216,8 @@
       <c r="E76" s="12">
         <v>0</v>
       </c>
-      <c r="F76" s="7"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A77" s="12">
         <v>4590900</v>
       </c>
@@ -2445,10 +2231,23 @@
       <c r="E77" s="12">
         <v>0</v>
       </c>
-      <c r="F77" s="7"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A78" s="9">
+        <v>5500100</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C78" s="7"/>
+      <c r="D78" s="9">
+        <v>955001001</v>
+      </c>
+      <c r="E78" s="9">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E74" xr:uid="{85CB23A7-FBFE-4C22-A658-7D7AF331C130}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06B66ED3-BEC6-4779-AA92-A4E1B8BDDFDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B18A87F8-BB09-42C9-A126-DB0119D2A0B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attr_skill_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="90">
   <si>
     <t>击中回血固定值</t>
   </si>
@@ -337,6 +337,14 @@
   </si>
   <si>
     <t>每8秒获得自身生命上限20%的护盾值，持续4秒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰弹</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷电</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -344,7 +352,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -431,6 +439,12 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="12">
@@ -566,7 +580,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -584,6 +598,9 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="3" xfId="4" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="差" xfId="3" builtinId="27"/>
@@ -922,13 +939,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85CB23A7-FBFE-4C22-A658-7D7AF331C130}">
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="64.625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
@@ -2247,6 +2264,48 @@
         <v>0</v>
       </c>
     </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A79" s="1">
+        <v>3010101</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D79" s="1">
+        <v>955001005</v>
+      </c>
+      <c r="E79" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A80" s="1">
+        <v>3020101</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D80" s="1">
+        <v>955001007</v>
+      </c>
+      <c r="E80" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A81" s="15">
+        <v>3030101</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D81" s="1">
+        <v>955001003</v>
+      </c>
+      <c r="E81" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B18A87F8-BB09-42C9-A126-DB0119D2A0B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05071DEB-96BC-4D13-8FA6-60F91B6434FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attr_skill_v8" sheetId="1" r:id="rId1"/>
@@ -2266,7 +2266,7 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
-        <v>3010101</v>
+        <v>3611800</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>88</v>
@@ -2280,7 +2280,7 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
-        <v>3020101</v>
+        <v>3611900</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>58</v>
@@ -2294,7 +2294,7 @@
     </row>
     <row r="81" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A81" s="15">
-        <v>3030101</v>
+        <v>3612000</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>89</v>

--- a/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05071DEB-96BC-4D13-8FA6-60F91B6434FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFCE3609-2B75-497E-8640-9EA23E717776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attr_skill_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_attr_skill_v8!$A$4:$E$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_attr_skill_v8!$A$4:$E$78</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="92">
   <si>
     <t>击中回血固定值</t>
   </si>
@@ -186,9 +186,6 @@
     <t>死亡时触发释放复活</t>
   </si>
   <si>
-    <t>复活时回复血郞、触发间隔、每轮挑战最大次数</t>
-  </si>
-  <si>
     <t>攻击次数触发释放多重打击</t>
   </si>
   <si>
@@ -346,6 +343,17 @@
   <si>
     <t>雷电</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>复活时回复血量、触发间隔、每轮挑战最大次数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻击中触发回血效果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻击中回血效果提高</t>
   </si>
 </sst>
 </file>
@@ -580,7 +588,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -601,6 +609,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="差" xfId="3" builtinId="27"/>
@@ -939,7 +948,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85CB23A7-FBFE-4C22-A658-7D7AF331C130}">
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E83"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" bestFit="1" customWidth="1"/>
@@ -1032,7 +1041,7 @@
         <v>3540100</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C6" s="7">
         <v>54010001</v>
@@ -1049,7 +1058,7 @@
         <v>3540300</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C7" s="7">
         <v>54030001</v>
@@ -1066,7 +1075,7 @@
         <v>3540500</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C8" s="7">
         <v>54050001</v>
@@ -1083,7 +1092,7 @@
         <v>3540700</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C9" s="7">
         <v>54070001</v>
@@ -1100,7 +1109,7 @@
         <v>3540900</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" s="7">
         <v>54090001</v>
@@ -1117,7 +1126,7 @@
         <v>3541100</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C11" s="7">
         <v>54110001</v>
@@ -1134,7 +1143,7 @@
         <v>3541300</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C12" s="7">
         <v>54130001</v>
@@ -1151,7 +1160,7 @@
         <v>3541500</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C13" s="7">
         <v>54150001</v>
@@ -1168,7 +1177,7 @@
         <v>3541700</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C14" s="7">
         <v>54170001</v>
@@ -1185,7 +1194,7 @@
         <v>3541900</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C15" s="7">
         <v>54190001</v>
@@ -1202,7 +1211,7 @@
         <v>3542100</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C16" s="7">
         <v>54210001</v>
@@ -1219,7 +1228,7 @@
         <v>3542300</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C17" s="7">
         <v>54230001</v>
@@ -1236,7 +1245,7 @@
         <v>3542500</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C18" s="7">
         <v>54250001</v>
@@ -1372,7 +1381,7 @@
         <v>3550300</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C26" s="7">
         <v>5000001</v>
@@ -1457,7 +1466,7 @@
         <v>3561000</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C31" s="7">
         <v>56100001</v>
@@ -1474,7 +1483,7 @@
         <v>3561300</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C32" s="7">
         <v>56130001</v>
@@ -1491,7 +1500,7 @@
         <v>3560300</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C33" s="7">
         <v>6000001</v>
@@ -1508,7 +1517,7 @@
         <v>3561200</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C34" s="7">
         <v>6010001</v>
@@ -1576,7 +1585,7 @@
         <v>3570800</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C38" s="7">
         <v>57060001</v>
@@ -1593,7 +1602,7 @@
         <v>3571000</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C39" s="7">
         <v>57100001</v>
@@ -1610,7 +1619,7 @@
         <v>3571200</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C40" s="7">
         <v>57120001</v>
@@ -1627,7 +1636,7 @@
         <v>3570300</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C41" s="7">
         <v>7000001</v>
@@ -1644,7 +1653,7 @@
         <v>3571400</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C42" s="7">
         <v>7010001</v>
@@ -1746,7 +1755,7 @@
         <v>3580300</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C48" s="7">
         <v>8000001</v>
@@ -1763,7 +1772,7 @@
         <v>3581000</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C49" s="7">
         <v>8010001</v>
@@ -1916,7 +1925,7 @@
         <v>3591800</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="C58" s="7">
         <v>59180001</v>
@@ -1933,7 +1942,7 @@
         <v>3592000</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C59" s="7">
         <v>59200001</v>
@@ -1950,7 +1959,7 @@
         <v>3591700</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60" s="7">
         <v>9000001</v>
@@ -1963,187 +1972,183 @@
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A61" s="11">
-        <v>3600100</v>
+      <c r="A61" s="9">
+        <v>3592200</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C61" s="7">
-        <v>60010001</v>
-      </c>
-      <c r="D61" s="11">
-        <v>0</v>
-      </c>
-      <c r="E61" s="11">
-        <v>600001</v>
+        <v>90</v>
+      </c>
+      <c r="C61" s="7"/>
+      <c r="D61" s="9">
+        <v>0</v>
+      </c>
+      <c r="E61" s="9">
+        <v>620001</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A62" s="11">
-        <v>3600300</v>
+      <c r="A62" s="16">
+        <v>3592300</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C62" s="7">
-        <v>60030001</v>
-      </c>
-      <c r="D62" s="11">
-        <v>60030001</v>
-      </c>
-      <c r="E62" s="11">
+        <v>91</v>
+      </c>
+      <c r="C62" s="7"/>
+      <c r="D62" s="16">
+        <v>59140001</v>
+      </c>
+      <c r="E62" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A63" s="11">
-        <v>3600600</v>
+        <v>3600100</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C63" s="7">
-        <v>60060001</v>
+        <v>60010001</v>
       </c>
       <c r="D63" s="11">
         <v>0</v>
       </c>
       <c r="E63" s="11">
-        <v>600002</v>
+        <v>600001</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A64" s="11">
-        <v>3600900</v>
+        <v>3600300</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C64" s="7">
-        <v>60090001</v>
+        <v>60030001</v>
       </c>
       <c r="D64" s="11">
-        <v>0</v>
+        <v>60030001</v>
       </c>
       <c r="E64" s="11">
-        <v>600003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A65" s="11">
-        <v>3601200</v>
+        <v>3600600</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C65" s="7">
-        <v>60110001</v>
+        <v>60060001</v>
       </c>
       <c r="D65" s="11">
-        <v>60110001</v>
+        <v>0</v>
       </c>
       <c r="E65" s="11">
-        <v>0</v>
+        <v>600002</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A66" s="11">
-        <v>3600500</v>
+        <v>3600900</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="C66" s="7">
-        <v>10010001</v>
+        <v>60090001</v>
       </c>
       <c r="D66" s="11">
-        <v>10010001</v>
+        <v>0</v>
       </c>
       <c r="E66" s="11">
-        <v>0</v>
+        <v>600003</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A67" s="11">
+        <v>3601200</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C67" s="7">
+        <v>60110001</v>
+      </c>
+      <c r="D67" s="11">
+        <v>60110001</v>
+      </c>
+      <c r="E67" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A68" s="11">
+        <v>3600500</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C68" s="7">
+        <v>10010001</v>
+      </c>
+      <c r="D68" s="11">
+        <v>10010001</v>
+      </c>
+      <c r="E68" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A69" s="11">
         <v>3600800</v>
       </c>
-      <c r="B67" s="7" t="s">
+      <c r="B69" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C67" s="7">
+      <c r="C69" s="7">
         <v>10020001</v>
       </c>
-      <c r="D67" s="11">
+      <c r="D69" s="11">
         <v>10020001</v>
       </c>
-      <c r="E67" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A68" s="12">
-        <v>3610200</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C68" s="7">
-        <v>61020001</v>
-      </c>
-      <c r="D68" s="12">
-        <v>0</v>
-      </c>
-      <c r="E68" s="12">
-        <v>610001</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A69" s="12">
-        <v>3610400</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C69" s="7">
-        <v>61040001</v>
-      </c>
-      <c r="D69" s="12">
-        <v>61040001</v>
-      </c>
-      <c r="E69" s="12">
+      <c r="E69" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A70" s="12">
-        <v>3610600</v>
+        <v>3610200</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="C70" s="7">
-        <v>61060001</v>
+        <v>61020001</v>
       </c>
       <c r="D70" s="12">
         <v>0</v>
       </c>
       <c r="E70" s="12">
-        <v>610002</v>
+        <v>610001</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A71" s="12">
-        <v>3610800</v>
+        <v>3610400</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C71" s="7">
-        <v>61080001</v>
+        <v>61040001</v>
       </c>
       <c r="D71" s="12">
-        <v>61080001</v>
+        <v>61040001</v>
       </c>
       <c r="E71" s="12">
         <v>0</v>
@@ -2151,33 +2156,33 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A72" s="12">
-        <v>3611000</v>
+        <v>3610600</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="C72" s="7">
-        <v>61100001</v>
+        <v>61060001</v>
       </c>
       <c r="D72" s="12">
-        <v>61100001</v>
+        <v>0</v>
       </c>
       <c r="E72" s="12">
-        <v>0</v>
+        <v>610002</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A73" s="12">
-        <v>3611200</v>
+        <v>3610800</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="C73" s="7">
-        <v>61120001</v>
+        <v>61080001</v>
       </c>
       <c r="D73" s="12">
-        <v>61120001</v>
+        <v>61080001</v>
       </c>
       <c r="E73" s="12">
         <v>0</v>
@@ -2185,124 +2190,158 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A74" s="12">
-        <v>3611400</v>
+        <v>3611000</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="C74" s="7">
-        <v>61140001</v>
+        <v>61100001</v>
       </c>
       <c r="D74" s="12">
-        <v>0</v>
+        <v>61100001</v>
       </c>
       <c r="E74" s="12">
-        <v>610003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A75" s="12">
-        <v>3611600</v>
+        <v>3611200</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C75" s="7">
-        <v>61160001</v>
+        <v>61120001</v>
       </c>
       <c r="D75" s="12">
-        <v>0</v>
+        <v>61120001</v>
       </c>
       <c r="E75" s="12">
-        <v>610004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A76" s="12">
-        <v>3610100</v>
+        <v>3611400</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="C76" s="7">
-        <v>11010001</v>
+        <v>61140001</v>
       </c>
       <c r="D76" s="12">
-        <v>11010001</v>
+        <v>0</v>
       </c>
       <c r="E76" s="12">
-        <v>0</v>
+        <v>610003</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A77" s="12">
+        <v>3611600</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C77" s="7">
+        <v>61160001</v>
+      </c>
+      <c r="D77" s="12">
+        <v>0</v>
+      </c>
+      <c r="E77" s="12">
+        <v>610004</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A78" s="12">
+        <v>3610100</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C78" s="7">
+        <v>11010001</v>
+      </c>
+      <c r="D78" s="12">
+        <v>11010001</v>
+      </c>
+      <c r="E78" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A79" s="12">
         <v>4590900</v>
       </c>
-      <c r="B77" s="7" t="s">
+      <c r="B79" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C79" s="7"/>
+      <c r="D79" s="12">
+        <v>30001</v>
+      </c>
+      <c r="E79" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A80" s="9">
+        <v>5500100</v>
+      </c>
+      <c r="B80" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C77" s="7"/>
-      <c r="D77" s="12">
-        <v>30001</v>
-      </c>
-      <c r="E77" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A78" s="9">
-        <v>5500100</v>
-      </c>
-      <c r="B78" s="7" t="s">
+      <c r="C80" s="7"/>
+      <c r="D80" s="9">
+        <v>955001001</v>
+      </c>
+      <c r="E80" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A81" s="1">
+        <v>3611800</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C78" s="7"/>
-      <c r="D78" s="9">
-        <v>955001001</v>
-      </c>
-      <c r="E78" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A79" s="1">
-        <v>3611800</v>
-      </c>
-      <c r="B79" s="1" t="s">
+      <c r="D81" s="1">
+        <v>955001005</v>
+      </c>
+      <c r="E81" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A82" s="1">
+        <v>3611900</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D82" s="1">
+        <v>955001007</v>
+      </c>
+      <c r="E82" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A83" s="15">
+        <v>3612000</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D79" s="1">
-        <v>955001005</v>
-      </c>
-      <c r="E79" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A80" s="1">
-        <v>3611900</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D80" s="1">
-        <v>955001007</v>
-      </c>
-      <c r="E80" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A81" s="15">
-        <v>3612000</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D81" s="1">
+      <c r="D83" s="1">
         <v>955001003</v>
       </c>
-      <c r="E81" s="1">
+      <c r="E83" s="1">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFCE3609-2B75-497E-8640-9EA23E717776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE129C7C-C805-437E-AFBD-00F49EC6582B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
   </bookViews>
@@ -588,7 +588,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -609,7 +609,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="差" xfId="3" builtinId="27"/>
@@ -1987,17 +1986,17 @@
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A62" s="16">
+      <c r="A62" s="10">
         <v>3592300</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>91</v>
       </c>
       <c r="C62" s="7"/>
-      <c r="D62" s="16">
-        <v>59140001</v>
-      </c>
-      <c r="E62" s="16">
+      <c r="D62" s="10">
+        <v>59280001</v>
+      </c>
+      <c r="E62" s="10">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE129C7C-C805-437E-AFBD-00F49EC6582B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E57A11F-72AB-49EC-AED3-6EA94BCF9F9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attr_skill_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="95">
   <si>
     <t>击中回血固定值</t>
   </si>
@@ -337,14 +337,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>冰弹</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>雷电</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>复活时回复血量、触发间隔、每轮挑战最大次数</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -354,6 +346,26 @@
   </si>
   <si>
     <t>普攻击中回血效果提高</t>
+  </si>
+  <si>
+    <t>每隔7秒，自动释放寒冰弹技能</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>每隔7秒，自动释放陨石技能</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>每隔6秒，自动释放雷击技能</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷击目标数量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷击伤害</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -449,10 +461,11 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="12">
@@ -606,9 +619,7 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="3" xfId="4" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="差" xfId="3" builtinId="27"/>
@@ -947,7 +958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85CB23A7-FBFE-4C22-A658-7D7AF331C130}">
-  <dimension ref="A1:E83"/>
+  <dimension ref="A1:E85"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" bestFit="1" customWidth="1"/>
@@ -1924,7 +1935,7 @@
         <v>3591800</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C58" s="7">
         <v>59180001</v>
@@ -1975,7 +1986,7 @@
         <v>3592200</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C61" s="7"/>
       <c r="D61" s="9">
@@ -1990,7 +2001,7 @@
         <v>3592300</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C62" s="7"/>
       <c r="D62" s="10">
@@ -2303,44 +2314,75 @@
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A81" s="1">
-        <v>3611800</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D81" s="1">
-        <v>955001005</v>
-      </c>
-      <c r="E81" s="1">
+      <c r="A81" s="15">
+        <v>5000100</v>
+      </c>
+      <c r="B81" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C81" s="15"/>
+      <c r="D81" s="15">
+        <v>95000100</v>
+      </c>
+      <c r="E81" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A82" s="1">
-        <v>3611900</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D82" s="1">
-        <v>955001007</v>
-      </c>
-      <c r="E82" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A82" s="15">
+        <v>5100100</v>
+      </c>
+      <c r="B82" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C82" s="15"/>
+      <c r="D82" s="15">
+        <v>95100100</v>
+      </c>
+      <c r="E82" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A83" s="15">
-        <v>3612000</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D83" s="1">
-        <v>955001003</v>
-      </c>
-      <c r="E83" s="1">
+        <v>5200100</v>
+      </c>
+      <c r="B83" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C83" s="15"/>
+      <c r="D83" s="15">
+        <v>95200100</v>
+      </c>
+      <c r="E83" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A84" s="15">
+        <v>5200300</v>
+      </c>
+      <c r="B84" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D84" s="15">
+        <v>95200300</v>
+      </c>
+      <c r="E84" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A85" s="15">
+        <v>5200500</v>
+      </c>
+      <c r="B85" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D85" s="15">
+        <v>95200500</v>
+      </c>
+      <c r="E85" s="1">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E57A11F-72AB-49EC-AED3-6EA94BCF9F9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6488F03-D414-44B6-9206-0056FB226845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="98">
   <si>
     <t>击中回血固定值</t>
   </si>
@@ -365,6 +365,18 @@
   </si>
   <si>
     <t>雷击伤害</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒冰弹技能</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石技能</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷击技能</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -958,7 +970,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85CB23A7-FBFE-4C22-A658-7D7AF331C130}">
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:E88"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" bestFit="1" customWidth="1"/>
@@ -2330,14 +2342,14 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A82" s="15">
-        <v>5100100</v>
+        <v>5000101</v>
       </c>
       <c r="B82" s="15" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C82" s="15"/>
       <c r="D82" s="15">
-        <v>95100100</v>
+        <v>95000101</v>
       </c>
       <c r="E82" s="15">
         <v>0</v>
@@ -2345,14 +2357,14 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A83" s="15">
-        <v>5200100</v>
+        <v>5100100</v>
       </c>
       <c r="B83" s="15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C83" s="15"/>
       <c r="D83" s="15">
-        <v>95200100</v>
+        <v>95100100</v>
       </c>
       <c r="E83" s="15">
         <v>0</v>
@@ -2360,29 +2372,74 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A84" s="15">
-        <v>5200300</v>
+        <v>5100101</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>93</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="C84" s="15"/>
       <c r="D84" s="15">
-        <v>95200300</v>
-      </c>
-      <c r="E84" s="1">
+        <v>95100101</v>
+      </c>
+      <c r="E84" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A85" s="15">
+        <v>5200100</v>
+      </c>
+      <c r="B85" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C85" s="15"/>
+      <c r="D85" s="15">
+        <v>95200100</v>
+      </c>
+      <c r="E85" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A86" s="15">
+        <v>5200101</v>
+      </c>
+      <c r="B86" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="C86" s="15"/>
+      <c r="D86" s="15">
+        <v>95200101</v>
+      </c>
+      <c r="E86" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A87" s="15">
+        <v>5200300</v>
+      </c>
+      <c r="B87" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D87" s="15">
+        <v>95200300</v>
+      </c>
+      <c r="E87" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A88" s="15">
         <v>5200500</v>
       </c>
-      <c r="B85" s="15" t="s">
+      <c r="B88" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="D85" s="15">
+      <c r="D88" s="15">
         <v>95200500</v>
       </c>
-      <c r="E85" s="1">
+      <c r="E88" s="1">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6488F03-D414-44B6-9206-0056FB226845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4CF1AF-292A-4DEE-8C6A-695E82D9F6B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attr_skill_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="102">
   <si>
     <t>击中回血固定值</t>
   </si>
@@ -377,6 +377,22 @@
   </si>
   <si>
     <t>雷击技能</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰弹数量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰弹伤害</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰弹范围</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>追加冰弹次数&amp;伤害</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -970,7 +986,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85CB23A7-FBFE-4C22-A658-7D7AF331C130}">
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:E92"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" bestFit="1" customWidth="1"/>
@@ -2417,13 +2433,13 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A87" s="15">
-        <v>5200300</v>
+        <v>5000300</v>
       </c>
       <c r="B87" s="15" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D87" s="15">
-        <v>95200300</v>
+        <v>95000300</v>
       </c>
       <c r="E87" s="1">
         <v>0</v>
@@ -2431,15 +2447,71 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A88" s="15">
+        <v>5000500</v>
+      </c>
+      <c r="B88" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="D88" s="15">
+        <v>95000500</v>
+      </c>
+      <c r="E88" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A89" s="15">
+        <v>5000700</v>
+      </c>
+      <c r="B89" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="D89" s="15">
+        <v>95000700</v>
+      </c>
+      <c r="E89" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A90" s="15">
+        <v>5000900</v>
+      </c>
+      <c r="B90" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="D90" s="15">
+        <v>95000900</v>
+      </c>
+      <c r="E90" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A91" s="15">
+        <v>5200300</v>
+      </c>
+      <c r="B91" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D91" s="15">
+        <v>95200300</v>
+      </c>
+      <c r="E91" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A92" s="15">
         <v>5200500</v>
       </c>
-      <c r="B88" s="15" t="s">
+      <c r="B92" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="D88" s="15">
+      <c r="D92" s="15">
         <v>95200500</v>
       </c>
-      <c r="E88" s="1">
+      <c r="E92" s="1">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4CF1AF-292A-4DEE-8C6A-695E82D9F6B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F89BA21-29D0-4A36-9A05-84E90CA23B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
   </bookViews>
@@ -1081,11 +1081,9 @@
       <c r="B6" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="7">
-        <v>54010001</v>
-      </c>
+      <c r="C6" s="7"/>
       <c r="D6" s="14">
-        <v>54010001</v>
+        <v>54010051</v>
       </c>
       <c r="E6" s="14">
         <v>0</v>
@@ -1098,11 +1096,9 @@
       <c r="B7" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="7">
-        <v>54030001</v>
-      </c>
+      <c r="C7" s="7"/>
       <c r="D7" s="14">
-        <v>54030001</v>
+        <v>54030051</v>
       </c>
       <c r="E7" s="14">
         <v>0</v>
@@ -1115,11 +1111,9 @@
       <c r="B8" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="7">
-        <v>54050001</v>
-      </c>
+      <c r="C8" s="7"/>
       <c r="D8" s="14">
-        <v>54050001</v>
+        <v>54050051</v>
       </c>
       <c r="E8" s="14">
         <v>0</v>
@@ -1132,11 +1126,9 @@
       <c r="B9" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="7">
-        <v>54070001</v>
-      </c>
+      <c r="C9" s="7"/>
       <c r="D9" s="14">
-        <v>54070001</v>
+        <v>54070051</v>
       </c>
       <c r="E9" s="14">
         <v>0</v>
@@ -1149,11 +1141,9 @@
       <c r="B10" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="7">
-        <v>54090001</v>
-      </c>
+      <c r="C10" s="7"/>
       <c r="D10" s="14">
-        <v>54090001</v>
+        <v>54090051</v>
       </c>
       <c r="E10" s="14">
         <v>0</v>
@@ -1166,11 +1156,9 @@
       <c r="B11" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="7">
-        <v>54110001</v>
-      </c>
+      <c r="C11" s="7"/>
       <c r="D11" s="14">
-        <v>54110001</v>
+        <v>54110051</v>
       </c>
       <c r="E11" s="14">
         <v>0</v>
@@ -1183,11 +1171,9 @@
       <c r="B12" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="7">
-        <v>54130001</v>
-      </c>
+      <c r="C12" s="7"/>
       <c r="D12" s="14">
-        <v>54130001</v>
+        <v>54130051</v>
       </c>
       <c r="E12" s="14">
         <v>0</v>
@@ -1200,11 +1186,9 @@
       <c r="B13" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C13" s="7">
-        <v>54150001</v>
-      </c>
+      <c r="C13" s="7"/>
       <c r="D13" s="14">
-        <v>54150001</v>
+        <v>54150051</v>
       </c>
       <c r="E13" s="14">
         <v>0</v>
@@ -1217,11 +1201,9 @@
       <c r="B14" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="7">
-        <v>54170001</v>
-      </c>
+      <c r="C14" s="7"/>
       <c r="D14" s="14">
-        <v>54170001</v>
+        <v>54170051</v>
       </c>
       <c r="E14" s="14">
         <v>0</v>
@@ -1234,11 +1216,9 @@
       <c r="B15" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="7">
-        <v>54190001</v>
-      </c>
+      <c r="C15" s="7"/>
       <c r="D15" s="14">
-        <v>54190001</v>
+        <v>54190051</v>
       </c>
       <c r="E15" s="14">
         <v>0</v>
@@ -1251,11 +1231,9 @@
       <c r="B16" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C16" s="7">
-        <v>54210001</v>
-      </c>
+      <c r="C16" s="7"/>
       <c r="D16" s="14">
-        <v>54210001</v>
+        <v>54210051</v>
       </c>
       <c r="E16" s="14">
         <v>0</v>
@@ -1268,11 +1246,9 @@
       <c r="B17" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C17" s="7">
-        <v>54230001</v>
-      </c>
+      <c r="C17" s="7"/>
       <c r="D17" s="14">
-        <v>54230001</v>
+        <v>54230051</v>
       </c>
       <c r="E17" s="14">
         <v>0</v>
@@ -1285,11 +1261,9 @@
       <c r="B18" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="7">
-        <v>54250001</v>
-      </c>
+      <c r="C18" s="7"/>
       <c r="D18" s="14">
-        <v>54250001</v>
+        <v>54250051</v>
       </c>
       <c r="E18" s="14">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F89BA21-29D0-4A36-9A05-84E90CA23B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22452F48-EE1F-4963-B2DE-AA1BF123FD15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
   </bookViews>
@@ -392,7 +392,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>追加冰弹次数&amp;伤害</t>
+    <t>追加冰弹次数</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22452F48-EE1F-4963-B2DE-AA1BF123FD15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4227A6-6715-40B6-8B10-D5D7F099B53B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attr_skill_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="103">
   <si>
     <t>击中回血固定值</t>
   </si>
@@ -393,6 +393,10 @@
   </si>
   <si>
     <t>追加冰弹次数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>追加冰爆</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -986,7 +990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85CB23A7-FBFE-4C22-A658-7D7AF331C130}">
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:E93"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" bestFit="1" customWidth="1"/>
@@ -2463,13 +2467,13 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A91" s="15">
-        <v>5200300</v>
+        <v>5001300</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="D91" s="15">
-        <v>95200300</v>
+        <v>95001300</v>
       </c>
       <c r="E91" s="1">
         <v>0</v>
@@ -2477,15 +2481,29 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A92" s="15">
+        <v>5200300</v>
+      </c>
+      <c r="B92" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D92" s="15">
+        <v>95200300</v>
+      </c>
+      <c r="E92" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A93" s="15">
         <v>5200500</v>
       </c>
-      <c r="B92" s="15" t="s">
+      <c r="B93" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="D92" s="15">
+      <c r="D93" s="15">
         <v>95200500</v>
       </c>
-      <c r="E92" s="1">
+      <c r="E93" s="1">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4227A6-6715-40B6-8B10-D5D7F099B53B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07948C13-DD52-4757-8179-39B586B1AB4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attr_skill_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="104">
   <si>
     <t>击中回血固定值</t>
   </si>
@@ -397,6 +397,10 @@
   </si>
   <si>
     <t>追加冰爆</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷击概率附加麻痹</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -990,7 +994,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85CB23A7-FBFE-4C22-A658-7D7AF331C130}">
-  <dimension ref="A1:E93"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" bestFit="1" customWidth="1"/>
@@ -2507,6 +2511,20 @@
         <v>0</v>
       </c>
     </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A94" s="15">
+        <v>5200700</v>
+      </c>
+      <c r="B94" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D94" s="15">
+        <v>95200700</v>
+      </c>
+      <c r="E94" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07948C13-DD52-4757-8179-39B586B1AB4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E27B9AA4-4B80-48E7-862D-F55AB10DEDB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attr_skill_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="108">
   <si>
     <t>击中回血固定值</t>
   </si>
@@ -402,6 +402,18 @@
   <si>
     <t>雷击概率附加麻痹</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石额外范围</t>
+  </si>
+  <si>
+    <t>陨石伤害</t>
+  </si>
+  <si>
+    <t>陨石数量</t>
+  </si>
+  <si>
+    <t>陨石落地后产生冲击波</t>
   </si>
 </sst>
 </file>
@@ -994,7 +1006,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85CB23A7-FBFE-4C22-A658-7D7AF331C130}">
-  <dimension ref="A1:E94"/>
+  <dimension ref="A1:E98"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" bestFit="1" customWidth="1"/>
@@ -2355,73 +2367,69 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A83" s="15">
-        <v>5100100</v>
+        <v>5000300</v>
       </c>
       <c r="B83" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="C83" s="15"/>
+        <v>98</v>
+      </c>
       <c r="D83" s="15">
-        <v>95100100</v>
-      </c>
-      <c r="E83" s="15">
+        <v>95000300</v>
+      </c>
+      <c r="E83" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A84" s="15">
-        <v>5100101</v>
+        <v>5000500</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="C84" s="15"/>
+        <v>99</v>
+      </c>
       <c r="D84" s="15">
-        <v>95100101</v>
-      </c>
-      <c r="E84" s="15">
+        <v>95000500</v>
+      </c>
+      <c r="E84" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A85" s="15">
-        <v>5200100</v>
+        <v>5000700</v>
       </c>
       <c r="B85" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="C85" s="15"/>
+        <v>100</v>
+      </c>
       <c r="D85" s="15">
-        <v>95200100</v>
-      </c>
-      <c r="E85" s="15">
+        <v>95000700</v>
+      </c>
+      <c r="E85" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A86" s="15">
-        <v>5200101</v>
+        <v>5000900</v>
       </c>
       <c r="B86" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="C86" s="15"/>
+        <v>101</v>
+      </c>
       <c r="D86" s="15">
-        <v>95200101</v>
-      </c>
-      <c r="E86" s="15">
+        <v>95000900</v>
+      </c>
+      <c r="E86" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A87" s="15">
-        <v>5000300</v>
+        <v>5001300</v>
       </c>
       <c r="B87" s="15" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D87" s="15">
-        <v>95000300</v>
+        <v>95001300</v>
       </c>
       <c r="E87" s="1">
         <v>0</v>
@@ -2429,41 +2437,43 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A88" s="15">
-        <v>5000500</v>
+        <v>5100100</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>99</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="C88" s="15"/>
       <c r="D88" s="15">
-        <v>95000500</v>
-      </c>
-      <c r="E88" s="1">
+        <v>95100100</v>
+      </c>
+      <c r="E88" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A89" s="15">
-        <v>5000700</v>
+        <v>5100101</v>
       </c>
       <c r="B89" s="15" t="s">
-        <v>100</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="C89" s="15"/>
       <c r="D89" s="15">
-        <v>95000700</v>
-      </c>
-      <c r="E89" s="1">
+        <v>95100101</v>
+      </c>
+      <c r="E89" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A90" s="15">
-        <v>5000900</v>
+        <v>5100300</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D90" s="15">
-        <v>95000900</v>
+        <v>95100300</v>
       </c>
       <c r="E90" s="1">
         <v>0</v>
@@ -2471,13 +2481,13 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A91" s="15">
-        <v>5001300</v>
+        <v>5100500</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D91" s="15">
-        <v>95001300</v>
+        <v>95100500</v>
       </c>
       <c r="E91" s="1">
         <v>0</v>
@@ -2485,13 +2495,13 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A92" s="15">
-        <v>5200300</v>
+        <v>5100700</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="D92" s="15">
-        <v>95200300</v>
+        <v>95100700</v>
       </c>
       <c r="E92" s="1">
         <v>0</v>
@@ -2499,13 +2509,13 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A93" s="15">
-        <v>5200500</v>
+        <v>5100900</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="D93" s="15">
-        <v>95200500</v>
+        <v>95100900</v>
       </c>
       <c r="E93" s="1">
         <v>0</v>
@@ -2513,15 +2523,73 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A94" s="15">
+        <v>5200100</v>
+      </c>
+      <c r="B94" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C94" s="15"/>
+      <c r="D94" s="15">
+        <v>95200100</v>
+      </c>
+      <c r="E94" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A95" s="15">
+        <v>5200101</v>
+      </c>
+      <c r="B95" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="C95" s="15"/>
+      <c r="D95" s="15">
+        <v>95200101</v>
+      </c>
+      <c r="E95" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A96" s="15">
+        <v>5200300</v>
+      </c>
+      <c r="B96" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D96" s="15">
+        <v>95200300</v>
+      </c>
+      <c r="E96" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A97" s="15">
+        <v>5200500</v>
+      </c>
+      <c r="B97" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D97" s="15">
+        <v>95200500</v>
+      </c>
+      <c r="E97" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A98" s="15">
         <v>5200700</v>
       </c>
-      <c r="B94" s="15" t="s">
+      <c r="B98" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="D94" s="15">
+      <c r="D98" s="15">
         <v>95200700</v>
       </c>
-      <c r="E94" s="1">
+      <c r="E98" s="1">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E27B9AA4-4B80-48E7-862D-F55AB10DEDB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F299FE4-2FAE-4CDA-9DBE-B97F4006F2E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="112">
   <si>
     <t>击中回血固定值</t>
   </si>
@@ -348,18 +348,6 @@
     <t>普攻击中回血效果提高</t>
   </si>
   <si>
-    <t>每隔7秒，自动释放寒冰弹技能</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>每隔7秒，自动释放陨石技能</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>每隔6秒，自动释放雷击技能</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>雷击目标数量</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -414,6 +402,31 @@
   </si>
   <si>
     <t>陨石落地后产生冲击波</t>
+  </si>
+  <si>
+    <t>冰弹CD</t>
+  </si>
+  <si>
+    <t>每隔7秒，自动获得陨石技能</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>每隔7秒，自动获得寒冰弹技能</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>每隔6秒，自动获得雷击技能</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石CD</t>
+  </si>
+  <si>
+    <t>雷击CD</t>
+  </si>
+  <si>
+    <t>普攻伤害</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1006,7 +1019,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85CB23A7-FBFE-4C22-A658-7D7AF331C130}">
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" bestFit="1" customWidth="1"/>
@@ -2340,7 +2353,7 @@
         <v>5000100</v>
       </c>
       <c r="B81" s="15" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="C81" s="15"/>
       <c r="D81" s="15">
@@ -2355,7 +2368,7 @@
         <v>5000101</v>
       </c>
       <c r="B82" s="15" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C82" s="15"/>
       <c r="D82" s="15">
@@ -2370,7 +2383,7 @@
         <v>5000300</v>
       </c>
       <c r="B83" s="15" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D83" s="15">
         <v>95000300</v>
@@ -2384,7 +2397,7 @@
         <v>5000500</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D84" s="15">
         <v>95000500</v>
@@ -2398,7 +2411,7 @@
         <v>5000700</v>
       </c>
       <c r="B85" s="15" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D85" s="15">
         <v>95000700</v>
@@ -2412,7 +2425,7 @@
         <v>5000900</v>
       </c>
       <c r="B86" s="15" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D86" s="15">
         <v>95000900</v>
@@ -2426,7 +2439,7 @@
         <v>5001300</v>
       </c>
       <c r="B87" s="15" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D87" s="15">
         <v>95001300</v>
@@ -2437,29 +2450,28 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A88" s="15">
-        <v>5100100</v>
+        <v>5020300</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="C88" s="15"/>
+        <v>105</v>
+      </c>
       <c r="D88" s="15">
-        <v>95100100</v>
-      </c>
-      <c r="E88" s="15">
+        <v>95020300</v>
+      </c>
+      <c r="E88" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A89" s="15">
-        <v>5100101</v>
+        <v>5100100</v>
       </c>
       <c r="B89" s="15" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C89" s="15"/>
       <c r="D89" s="15">
-        <v>95100101</v>
+        <v>95100100</v>
       </c>
       <c r="E89" s="15">
         <v>0</v>
@@ -2467,27 +2479,28 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A90" s="15">
-        <v>5100300</v>
+        <v>5100101</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>104</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="C90" s="15"/>
       <c r="D90" s="15">
-        <v>95100300</v>
-      </c>
-      <c r="E90" s="1">
+        <v>95100101</v>
+      </c>
+      <c r="E90" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A91" s="15">
-        <v>5100500</v>
+        <v>5100300</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D91" s="15">
-        <v>95100500</v>
+        <v>95100300</v>
       </c>
       <c r="E91" s="1">
         <v>0</v>
@@ -2495,13 +2508,13 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A92" s="15">
-        <v>5100700</v>
+        <v>5100500</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D92" s="15">
-        <v>95100700</v>
+        <v>95100500</v>
       </c>
       <c r="E92" s="1">
         <v>0</v>
@@ -2509,13 +2522,13 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A93" s="15">
-        <v>5100900</v>
+        <v>5100700</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D93" s="15">
-        <v>95100900</v>
+        <v>95100700</v>
       </c>
       <c r="E93" s="1">
         <v>0</v>
@@ -2523,73 +2536,130 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A94" s="15">
-        <v>5200100</v>
+        <v>5100900</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="C94" s="15"/>
+        <v>104</v>
+      </c>
       <c r="D94" s="15">
-        <v>95200100</v>
-      </c>
-      <c r="E94" s="15">
+        <v>95100900</v>
+      </c>
+      <c r="E94" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A95" s="15">
-        <v>5200101</v>
+        <v>5120300</v>
       </c>
       <c r="B95" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="C95" s="15"/>
+        <v>109</v>
+      </c>
       <c r="D95" s="15">
-        <v>95200101</v>
-      </c>
-      <c r="E95" s="15">
+        <v>95120300</v>
+      </c>
+      <c r="E95" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A96" s="15">
-        <v>5200300</v>
+        <v>5200100</v>
       </c>
       <c r="B96" s="15" t="s">
-        <v>93</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="C96" s="15"/>
       <c r="D96" s="15">
-        <v>95200300</v>
-      </c>
-      <c r="E96" s="1">
+        <v>95200100</v>
+      </c>
+      <c r="E96" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A97" s="15">
-        <v>5200500</v>
+        <v>5200101</v>
       </c>
       <c r="B97" s="15" t="s">
         <v>94</v>
       </c>
+      <c r="C97" s="15"/>
       <c r="D97" s="15">
-        <v>95200500</v>
-      </c>
-      <c r="E97" s="1">
+        <v>95200101</v>
+      </c>
+      <c r="E97" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A98" s="15">
+        <v>5200300</v>
+      </c>
+      <c r="B98" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="D98" s="15">
+        <v>95200300</v>
+      </c>
+      <c r="E98" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A99" s="15">
+        <v>5200500</v>
+      </c>
+      <c r="B99" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="D99" s="15">
+        <v>95200500</v>
+      </c>
+      <c r="E99" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A100" s="15">
         <v>5200700</v>
       </c>
-      <c r="B98" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="D98" s="15">
+      <c r="B100" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="D100" s="15">
         <v>95200700</v>
       </c>
-      <c r="E98" s="1">
+      <c r="E100" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A101" s="15">
+        <v>5220300</v>
+      </c>
+      <c r="B101" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D101" s="15">
+        <v>95220300</v>
+      </c>
+      <c r="E101" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A102" s="15">
+        <v>7000100</v>
+      </c>
+      <c r="B102" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C102" s="15"/>
+      <c r="D102" s="15">
+        <v>97000100</v>
+      </c>
+      <c r="E102" s="15">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F299FE4-2FAE-4CDA-9DBE-B97F4006F2E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F7929E-6A9E-443F-83F3-17400C78F1AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attr_skill_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="114">
   <si>
     <t>击中回血固定值</t>
   </si>
@@ -426,6 +426,14 @@
   </si>
   <si>
     <t>普攻伤害</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰弹概率附加冰冻</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石概率附加燃烧</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1019,7 +1027,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85CB23A7-FBFE-4C22-A658-7D7AF331C130}">
-  <dimension ref="A1:E102"/>
+  <dimension ref="A1:E104"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" bestFit="1" customWidth="1"/>
@@ -2450,13 +2458,13 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A88" s="15">
-        <v>5020300</v>
+        <v>5001500</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="D88" s="15">
-        <v>95020300</v>
+        <v>95001500</v>
       </c>
       <c r="E88" s="1">
         <v>0</v>
@@ -2464,29 +2472,28 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A89" s="15">
-        <v>5100100</v>
+        <v>5020300</v>
       </c>
       <c r="B89" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="C89" s="15"/>
+        <v>105</v>
+      </c>
       <c r="D89" s="15">
-        <v>95100100</v>
-      </c>
-      <c r="E89" s="15">
+        <v>95020300</v>
+      </c>
+      <c r="E89" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A90" s="15">
-        <v>5100101</v>
+        <v>5100100</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C90" s="15"/>
       <c r="D90" s="15">
-        <v>95100101</v>
+        <v>95100100</v>
       </c>
       <c r="E90" s="15">
         <v>0</v>
@@ -2494,27 +2501,28 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A91" s="15">
-        <v>5100300</v>
+        <v>5100101</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>101</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="C91" s="15"/>
       <c r="D91" s="15">
-        <v>95100300</v>
-      </c>
-      <c r="E91" s="1">
+        <v>95100101</v>
+      </c>
+      <c r="E91" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A92" s="15">
-        <v>5100500</v>
+        <v>5100300</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D92" s="15">
-        <v>95100500</v>
+        <v>95100300</v>
       </c>
       <c r="E92" s="1">
         <v>0</v>
@@ -2522,13 +2530,13 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A93" s="15">
-        <v>5100700</v>
+        <v>5100500</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D93" s="15">
-        <v>95100700</v>
+        <v>95100500</v>
       </c>
       <c r="E93" s="1">
         <v>0</v>
@@ -2536,13 +2544,13 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A94" s="15">
-        <v>5100900</v>
+        <v>5100700</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D94" s="15">
-        <v>95100900</v>
+        <v>95100700</v>
       </c>
       <c r="E94" s="1">
         <v>0</v>
@@ -2550,13 +2558,13 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A95" s="15">
-        <v>5120300</v>
+        <v>5100900</v>
       </c>
       <c r="B95" s="15" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D95" s="15">
-        <v>95120300</v>
+        <v>95100900</v>
       </c>
       <c r="E95" s="1">
         <v>0</v>
@@ -2564,71 +2572,71 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A96" s="15">
-        <v>5200100</v>
+        <v>5101100</v>
       </c>
       <c r="B96" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="C96" s="15"/>
+        <v>113</v>
+      </c>
       <c r="D96" s="15">
-        <v>95200100</v>
-      </c>
-      <c r="E96" s="15">
+        <v>95101100</v>
+      </c>
+      <c r="E96" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A97" s="15">
-        <v>5200101</v>
+        <v>5120300</v>
       </c>
       <c r="B97" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="C97" s="15"/>
+        <v>109</v>
+      </c>
       <c r="D97" s="15">
-        <v>95200101</v>
-      </c>
-      <c r="E97" s="15">
+        <v>95120300</v>
+      </c>
+      <c r="E97" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A98" s="15">
-        <v>5200300</v>
+        <v>5200100</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>90</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="C98" s="15"/>
       <c r="D98" s="15">
-        <v>95200300</v>
-      </c>
-      <c r="E98" s="1">
+        <v>95200100</v>
+      </c>
+      <c r="E98" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A99" s="15">
-        <v>5200500</v>
+        <v>5200101</v>
       </c>
       <c r="B99" s="15" t="s">
-        <v>91</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="C99" s="15"/>
       <c r="D99" s="15">
-        <v>95200500</v>
-      </c>
-      <c r="E99" s="1">
+        <v>95200101</v>
+      </c>
+      <c r="E99" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A100" s="15">
-        <v>5200700</v>
+        <v>5200300</v>
       </c>
       <c r="B100" s="15" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D100" s="15">
-        <v>95200700</v>
+        <v>95200300</v>
       </c>
       <c r="E100" s="1">
         <v>0</v>
@@ -2636,13 +2644,13 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A101" s="15">
-        <v>5220300</v>
+        <v>5200500</v>
       </c>
       <c r="B101" s="15" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="D101" s="15">
-        <v>95220300</v>
+        <v>95200500</v>
       </c>
       <c r="E101" s="1">
         <v>0</v>
@@ -2650,16 +2658,44 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A102" s="15">
+        <v>5200700</v>
+      </c>
+      <c r="B102" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="D102" s="15">
+        <v>95200700</v>
+      </c>
+      <c r="E102" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A103" s="15">
+        <v>5220300</v>
+      </c>
+      <c r="B103" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D103" s="15">
+        <v>95220300</v>
+      </c>
+      <c r="E103" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A104" s="15">
         <v>7000100</v>
       </c>
-      <c r="B102" s="15" t="s">
+      <c r="B104" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C102" s="15"/>
-      <c r="D102" s="15">
+      <c r="C104" s="15"/>
+      <c r="D104" s="15">
         <v>97000100</v>
       </c>
-      <c r="E102" s="15">
+      <c r="E104" s="15">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F7929E-6A9E-443F-83F3-17400C78F1AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{198BE1C1-C3F6-48DF-835F-931BB2017747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attr_skill_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="117">
   <si>
     <t>击中回血固定值</t>
   </si>
@@ -434,6 +434,18 @@
   </si>
   <si>
     <t>陨石概率附加燃烧</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻附加燃烧</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻附加概率冰冻</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻附加概率麻痹</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1027,7 +1039,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85CB23A7-FBFE-4C22-A658-7D7AF331C130}">
-  <dimension ref="A1:E104"/>
+  <dimension ref="A1:E107"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" bestFit="1" customWidth="1"/>
@@ -2699,6 +2711,49 @@
         <v>0</v>
       </c>
     </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A105" s="15">
+        <v>7000501</v>
+      </c>
+      <c r="B105" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="C105" s="15"/>
+      <c r="D105" s="15">
+        <v>0</v>
+      </c>
+      <c r="E105" s="15">
+        <v>630001</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A106" s="15">
+        <v>7000502</v>
+      </c>
+      <c r="B106" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="D106" s="1">
+        <v>0</v>
+      </c>
+      <c r="E106" s="15">
+        <v>640001</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A107" s="15">
+        <v>7000504</v>
+      </c>
+      <c r="B107" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D107" s="1">
+        <v>0</v>
+      </c>
+      <c r="E107" s="15">
+        <v>660001</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attr_skill_v8【迷宫-属性id关联技能id】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{198BE1C1-C3F6-48DF-835F-931BB2017747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F07D30-CA00-4441-8DD2-CD86DBF45935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{58DB412F-E489-42CA-A0E8-B22FB67DB1C8}"/>
   </bookViews>
@@ -2720,10 +2720,10 @@
       </c>
       <c r="C105" s="15"/>
       <c r="D105" s="15">
-        <v>0</v>
+        <v>95001500</v>
       </c>
       <c r="E105" s="15">
-        <v>630001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.15">
@@ -2733,11 +2733,11 @@
       <c r="B106" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="D106" s="1">
-        <v>0</v>
+      <c r="D106" s="15">
+        <v>95101100</v>
       </c>
       <c r="E106" s="15">
-        <v>640001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.15">
@@ -2747,11 +2747,11 @@
       <c r="B107" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="D107" s="1">
-        <v>0</v>
+      <c r="D107" s="15">
+        <v>95200700</v>
       </c>
       <c r="E107" s="15">
-        <v>660001</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
